--- a/data_input/monthly/2025-12.xlsx
+++ b/data_input/monthly/2025-12.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="voucher_month" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="booking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="voucher_month" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -622,12 +623,26 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              2 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">   booking                   41 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   voucher_month              2 dòng   bắt buộc: m, brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
@@ -639,6 +654,3100 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ev_month</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>outlet</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>etype</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>lost_reason</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>guests</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>exp_n</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>closed_n</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>inq_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>115</v>
+      </c>
+      <c r="N2" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>YEP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>130</v>
+      </c>
+      <c r="N3" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>70</v>
+      </c>
+      <c r="N4" t="n">
+        <v>56970000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>94</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>120</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>65</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Không liên lạc được</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>100</v>
+      </c>
+      <c r="N10" t="n">
+        <v>101833200</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Không liên lạc được</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>80</v>
+      </c>
+      <c r="N11" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>33800000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>45</v>
+      </c>
+      <c r="N13" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>70</v>
+      </c>
+      <c r="N15" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>45</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>YEP</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>40</v>
+      </c>
+      <c r="N17" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>40</v>
+      </c>
+      <c r="N20" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>YEP</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15415000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>15415000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Không gian / sức chứa</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13860000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ngân sách / chi phí</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10812690</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>10812690</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ngân sách / chi phí</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>30</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ngân sách / chi phí</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>40</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>15</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chụp hình / quay</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>20</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chụp hình / quay</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Khách đổi kế hoạch / hết nhu cầu</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>60</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data_input/monthly/2025-12.xlsx
+++ b/data_input/monthly/2025-12.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F3F2EE"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +57,11 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F1F26"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -78,6 +87,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3755,36 +3765,29 @@
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>disc</t>
         </is>

--- a/data_input/monthly/2025-12.xlsx
+++ b/data_input/monthly/2025-12.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="booking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="voucher_month" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="voucher_month" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data_input/monthly/2025-12.xlsx
+++ b/data_input/monthly/2025-12.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,12 +35,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00F3F2EE"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +53,6 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F1F26"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -87,7 +78,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3765,29 +3755,36 @@
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>disc</t>
         </is>

--- a/data_input/monthly/2025-12.xlsx
+++ b/data_input/monthly/2025-12.xlsx
@@ -633,7 +633,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                   41 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   booking                   40 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2335,22 +2335,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Lost</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Không gian / sức chứa</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>15000000</v>
+        <v>13860000</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2371,24 +2376,19 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NOIRE DINING</t>
+          <t>NOIRE ET</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Room rental</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2418,17 +2418,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Không gian / sức chứa</t>
+          <t>Ngân sách / chi phí</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N24" t="n">
-        <v>13860000</v>
+        <v>12000000</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2449,19 +2449,24 @@
           <t>2025-12</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NOIRE ET</t>
+          <t>NOIRE DINING</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2471,46 +2476,41 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Room rental</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MKT</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Ngân sách / chi phí</t>
+          <t>won</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N25" t="n">
-        <v>12000000</v>
+        <v>10812690</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>10812690</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NOIRE DINING</t>
+          <t>NOIRE ET</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2549,41 +2549,46 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>MKT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Lost</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ngân sách / chi phí</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N26" t="n">
-        <v>10812690</v>
+        <v>10000000</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>10812690</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2595,24 +2600,19 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NOIRE ET</t>
+          <t>NOIRE DINING</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2627,29 +2627,24 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MKT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Ngân sách / chi phí</t>
+          <t>open</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N27" t="n">
         <v>10000000</v>
@@ -2673,19 +2668,24 @@
           <t>2025-12</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NOIRE DINING</t>
+          <t>NOIRE ET</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Room rental</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>MKT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tentative</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2717,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N28" t="n">
         <v>10000000</v>
@@ -2743,22 +2743,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NOIRE ET</t>
+          <t>NOIRE DINING</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Room rental</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2778,19 +2778,24 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Lost</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ngân sách / chi phí</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
         <v>10000000</v>
@@ -2816,22 +2821,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NOIRE DINING</t>
+          <t>NOIRE ET</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2841,34 +2846,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MKT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Ngân sách / chi phí</t>
+          <t>won</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="N30" t="n">
         <v>10000000</v>
@@ -2877,10 +2877,10 @@
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2894,37 +2894,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NOIRE ET</t>
+          <t>NOIRE DINING</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>table</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>MKT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2941,16 +2941,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="N31" t="n">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -2965,34 +2965,29 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NOIRE DINING</t>
+          <t>NOIRE ET</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>event</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Room rental</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3002,31 +2997,31 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>open</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N32" t="n">
-        <v>8000000</v>
+        <v>6000000</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3038,6 +3033,11 @@
           <t>2025-12</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>NCB_ET</t>
@@ -3060,29 +3060,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Room rental</t>
+          <t>Chụp hình / quay</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MKT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tentative</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>won</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N33" t="n">
         <v>6000000</v>
@@ -3091,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3106,11 +3106,6 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>NCB_ET</t>
@@ -3133,29 +3128,29 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chụp hình / quay</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>MKT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>open</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N34" t="n">
         <v>6000000</v>
@@ -3164,10 +3159,10 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3179,19 +3174,24 @@
           <t>2025-12</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NOIRE ET</t>
+          <t>NOIRE DINING</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Chụp hình / quay</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3226,7 +3226,7 @@
         <v>10</v>
       </c>
       <c r="N35" t="n">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -3274,22 +3274,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chụp hình / quay</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MKT</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>won</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -3299,16 +3299,16 @@
         <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>4000000</v>
+        <v>3000000</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3322,22 +3322,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NOIRE DINING</t>
+          <t>NOIRE ET</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3352,36 +3352,36 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>MKT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>open</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3539,11 +3539,6 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>NCB_ET</t>
@@ -3576,7 +3571,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tentative</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3612,19 +3607,24 @@
           <t>2025-12</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NOIRE ET</t>
+          <t>NOIRE DINING</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3644,19 +3644,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Lost</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Khách đổi kế hoạch / hết nhu cầu</t>
         </is>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3671,84 +3676,6 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>NOIRE DINING</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>MKT</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Khách đổi kế hoạch / hết nhu cầu</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>60</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
         <v>0</v>
       </c>
     </row>
